--- a/SEMOBS_v3(Recuperado Automaticamente).xlsx
+++ b/SEMOBS_v3(Recuperado Automaticamente).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\planilhas\Monitoramento_de_mudas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391CA4FE-832B-446E-935B-22DA07179B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175D0A2A-609F-4B53-AF58-D217FEE147D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="916" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="916" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="359">
   <si>
     <t>SISTEMA DE MONITORAMENTO SEMOBS — CONTAGEM/MG</t>
   </si>
@@ -1161,13 +1161,79 @@
     <t>01/06,</t>
   </si>
   <si>
-    <t>02/06,</t>
-  </si>
-  <si>
     <t>03/06,</t>
   </si>
   <si>
     <t>10/06,</t>
+  </si>
+  <si>
+    <t>01/06, 04/06</t>
+  </si>
+  <si>
+    <t>03/06, 04/06</t>
+  </si>
+  <si>
+    <t>04/06, 10/06,</t>
+  </si>
+  <si>
+    <t>01/06, 02/06, 05/06</t>
+  </si>
+  <si>
+    <t>05/06,</t>
+  </si>
+  <si>
+    <t>03/06, 04/06, 05/06</t>
+  </si>
+  <si>
+    <t>01/06, 05/06</t>
+  </si>
+  <si>
+    <t>08/06,</t>
+  </si>
+  <si>
+    <t>01/06, 05/06,08/06</t>
+  </si>
+  <si>
+    <t>01/06, 05/06, 08/06</t>
+  </si>
+  <si>
+    <t>01/06, 08/06</t>
+  </si>
+  <si>
+    <t>01/06, 02/06, 09/06</t>
+  </si>
+  <si>
+    <t>09/06,</t>
+  </si>
+  <si>
+    <t>08/06, 09/06,</t>
+  </si>
+  <si>
+    <t>08/06, 09/06</t>
+  </si>
+  <si>
+    <t>01/06, 03/06, 05/06, 09/06</t>
+  </si>
+  <si>
+    <t>01/06, 03/06, 05/06, 09/06,</t>
+  </si>
+  <si>
+    <t>02/06, 09/06</t>
+  </si>
+  <si>
+    <t>02/06,10/06,</t>
+  </si>
+  <si>
+    <t>02/06, 10/06,</t>
+  </si>
+  <si>
+    <t>02/06, 05/06, 10/06,</t>
+  </si>
+  <si>
+    <t>02/06, 10/06</t>
+  </si>
+  <si>
+    <t>02/06, 09/06,</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1610,6 +1676,9 @@
     <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1700,22 +1769,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
+      <xdr:colOff>69851</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
+      <xdr:colOff>1220439</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
+        <xdr:cNvPr id="5" name="Imagem 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48CE25D9-F129-4B8C-477F-839EA152E49A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0740292-F94F-D6B5-9AB1-81169B2C2F9F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1731,8 +1800,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="123191" y="9259570"/>
-          <a:ext cx="1159351" cy="1544320"/>
+          <a:off x="136526" y="9040495"/>
+          <a:ext cx="1150588" cy="1521460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1750,13 +1819,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>10795</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1215042</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>1555115</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1764,7 +1833,7 @@
         <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F2091D-A550-F8A4-A05F-90E9D3A1EEC6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7272E4D-0E0F-6401-DA9A-9E1B02C3C841}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1780,8 +1849,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="123190" y="8573770"/>
+          <a:off x="123190" y="8116570"/>
           <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1390015</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>6985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1028352</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1536065</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C20740DE-BEC3-15B8-C277-1D900BB8A370}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1456690" y="8112760"/>
+          <a:ext cx="1143287" cy="1529080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1794,888 +1907,6 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56514</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>10794</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1214490</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>1555114</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADE3A35E-A8BF-6EB2-4508-E5EFD4DF790C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123189" y="9488169"/>
-          <a:ext cx="1157976" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215042</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A842D9B5-8536-7FEE-10D6-5DC292827BA5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="9030970"/>
-          <a:ext cx="1158527" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA64F40B-0A1B-6221-9B08-479F2CB8D393}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123191" y="8345170"/>
-          <a:ext cx="1159351" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215042</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08656714-591E-6D17-34EA-B076867EDE3D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="9259570"/>
-          <a:ext cx="1158527" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215042</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DE85C19-30E4-9D1E-8C99-922DED4272A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8573770"/>
-          <a:ext cx="1158527" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207E1752-AD05-4758-8A34-E66012E793BE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123191" y="9030970"/>
-          <a:ext cx="1159351" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>10794</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215315</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>1555114</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE1248CA-E938-F0FE-9BAB-E8C5DD27F697}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8802369"/>
-          <a:ext cx="1158800" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D9B63BA-0CEA-D867-664A-094CA1D07CB2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123191" y="8345170"/>
-          <a:ext cx="1159351" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215042</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71344CBC-AF68-919D-AFBC-E5E2D53FC269}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8573770"/>
-          <a:ext cx="1158527" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1214765</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13920F7A-E7FB-BC09-1822-733A5F4F3C11}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="10402570"/>
-          <a:ext cx="1158250" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46C13ABC-2425-7E76-DBC9-A8EB301E573D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123191" y="8116570"/>
-          <a:ext cx="1159351" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>10794</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215315</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>1555114</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614E9B69-A426-9FAE-B5C1-C101CEBDED10}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8802369"/>
-          <a:ext cx="1158800" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1214765</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA284A5E-8C7C-65A5-DC86-BD369EA26138}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8345170"/>
-          <a:ext cx="1158250" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1214765</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA217B4-25F0-21E8-A494-F750C1809638}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8573770"/>
-          <a:ext cx="1158250" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A882729-7910-2607-0790-CD152E57EB86}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123191" y="8345170"/>
-          <a:ext cx="1159351" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215042</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CA46A51-61BB-B143-9B2B-2566FB42708B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8573770"/>
-          <a:ext cx="1158527" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56516</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1215867</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFFD68E-85EB-0F24-E809-B51233168A46}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123191" y="9488170"/>
-          <a:ext cx="1159351" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>56515</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>10795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1214418</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1555115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CBBFA2A-DB31-40E6-1CF2-8E1BBC02948A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="123190" y="8345170"/>
-          <a:ext cx="1157903" cy="1544320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2765,10 +1996,235 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923876</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>11674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>314563</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1527419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7880E7FE-4EBC-82D1-F3FB-458D3A83FE67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2491838" y="9514693"/>
+          <a:ext cx="1171129" cy="1515745"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44789</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>12992</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>512225</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1534452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagem 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B4CC068-FC5E-BB6A-89E0-4CF0D18B3884}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4213808" y="9516011"/>
+          <a:ext cx="1156167" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>8890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1212221</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1553210</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagem 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B14DD2-5A2E-B1CE-617C-11BDCBDBA885}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="11362690"/>
+          <a:ext cx="1155705" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1209225</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1558925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagem 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED93FA4-0974-E1A0-DF22-96FA1E4ED60C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="13414375"/>
+          <a:ext cx="1152710" cy="1536700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56514</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214490</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1555114</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B662854-9DBA-EA3D-EBBB-45F6D518EB44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123189" y="10402569"/>
+          <a:ext cx="1157976" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2814,10 +2270,274 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1249045</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>898812</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C978E15E-33AC-6E94-BCF8-FB2465C5955D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1315720" y="7897495"/>
+          <a:ext cx="1154717" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>921386</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>310992</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA8BC48-AD4B-559E-090B-AA21C37CB636}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2493011" y="7897495"/>
+          <a:ext cx="1170781" cy="1525270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>8890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215701</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1553210</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagem 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E33C17E3-08D9-A9C0-D4C5-8AC950D56E7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9762490"/>
+          <a:ext cx="1159186" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214272</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1547495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA9D993B-9D71-18D8-DA25-F900388CAD59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="11633200"/>
+          <a:ext cx="1157757" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>45085</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1578610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1207147</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>3117215</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagem 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C489784-FAD4-878F-3AC5-3F28BD394B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="111760" y="9455785"/>
+          <a:ext cx="1162062" cy="1538605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>134620</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>18415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1542574</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagem 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{020163FE-E2CD-2FB8-BFC0-B8BAC88BB9C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4306570" y="7895590"/>
+          <a:ext cx="1141730" cy="1524159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2998,13 +2718,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1260475</xdr:colOff>
+      <xdr:colOff>1236228</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>6984</xdr:rowOff>
+      <xdr:rowOff>16509</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>908119</xdr:colOff>
+      <xdr:colOff>872442</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>1545589</xdr:rowOff>
     </xdr:to>
@@ -3029,8 +2749,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1327150" y="13094334"/>
-          <a:ext cx="1152594" cy="1538605"/>
+          <a:off x="1305501" y="13074418"/>
+          <a:ext cx="1142896" cy="1529080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3042,13 +2762,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1254760</xdr:colOff>
+      <xdr:colOff>1248872</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>6983</xdr:rowOff>
+      <xdr:rowOff>16508</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>914644</xdr:colOff>
+      <xdr:colOff>897326</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>1545588</xdr:rowOff>
     </xdr:to>
@@ -3073,8 +2793,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1321435" y="14970758"/>
-          <a:ext cx="1164834" cy="1538605"/>
+          <a:off x="1318145" y="14944781"/>
+          <a:ext cx="1155136" cy="1529080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3251,6 +2971,3579 @@
         <a:xfrm>
           <a:off x="5445760" y="13113383"/>
           <a:ext cx="1164834" cy="1538605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1237962</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>20319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>888437</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>1560829</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B66FBCA8-1FD7-667A-B5CF-FB7FF08B7009}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1307235" y="11207864"/>
+          <a:ext cx="1157157" cy="1540510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56514</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>12699</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1213629</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>1557019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73E0DD5A-0071-5F26-C582-88CF8311BBF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123189" y="13100049"/>
+          <a:ext cx="1157115" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>929174</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>17545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>341658</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>1546625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B198854E-9BCB-91F0-3399-AABC00B61E7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2505129" y="14945818"/>
+          <a:ext cx="1196256" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F2091D-A550-F8A4-A05F-90E9D3A1EEC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8573770"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1390015</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>6985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1045497</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1524635</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{315ED157-4312-EDCE-DE82-B6A4BDB32BA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1456690" y="8569960"/>
+          <a:ext cx="1160432" cy="1517650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56514</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>8889</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1213944</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1553209</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5499A6F-9389-A1DD-0BB6-A3DC5A71E833}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123189" y="10448289"/>
+          <a:ext cx="1157430" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214272</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1547495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B5BFF03-DC4E-0DA1-330D-9C26903608DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="12319000"/>
+          <a:ext cx="1157757" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1638C87D-D1F1-EDD7-EF49-214BF36929E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8802370"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214418</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCC694D2-922E-650E-0C2A-2E86EC04A0FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9030970"/>
+          <a:ext cx="1157903" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF835E1-EABD-04A8-D7BC-8BB27F669041}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="8802370"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9015EF4F-D81C-6895-6DC8-DF33A3E244B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9488170"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56514</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>10794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214490</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1555114</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADE3A35E-A8BF-6EB2-4508-E5EFD4DF790C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123189" y="9488169"/>
+          <a:ext cx="1157976" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1268095</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>908337</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8F9118B-1EF7-74B7-393B-615E6A09D403}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1334770" y="9497695"/>
+          <a:ext cx="1145192" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A842D9B5-8536-7FEE-10D6-5DC292827BA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9030970"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1250950</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>908337</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA28F81C-296D-CBEA-272F-01AC0D396814}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1317625" y="9036685"/>
+          <a:ext cx="1162337" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>961390</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>331122</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1BC4872-E448-4710-863F-DFC73C3A2598}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2533015" y="9040495"/>
+          <a:ext cx="1150907" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA64F40B-0A1B-6221-9B08-479F2CB8D393}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="8345170"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1249045</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>889287</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{305D701E-A936-0CAF-BDC2-3EE7D2364A61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1315720" y="8354695"/>
+          <a:ext cx="1145192" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56514</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>8889</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1213944</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1553209</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CA58BF5-4364-8E12-67E0-1F0475117E21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123189" y="10219689"/>
+          <a:ext cx="1157430" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214272</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1547495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagem 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E141ACD7-BA5C-61E3-0809-AE86FE648903}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="12090400"/>
+          <a:ext cx="1157757" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF54914-0223-4440-05BF-22385784D3ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8116570"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215315</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1555114</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D7B453F-E9BE-5C6D-01E2-1B656E86B6C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8116569"/>
+          <a:ext cx="1158800" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC96B40-A7D2-B510-1753-54279AC6E7C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8345170"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08656714-591E-6D17-34EA-B076867EDE3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9259570"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1249045</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>915957</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1DEAE27-BB35-311F-F353-ADF252682FFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1315720" y="9269095"/>
+          <a:ext cx="1171862" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA942F90-0F88-2CA1-4BDF-A22AE974809C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8802370"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DE85C19-30E4-9D1E-8C99-922DED4272A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8573770"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1266190</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>912147</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37D8F463-032F-DBAF-4F32-CB1A9A3061F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1332865" y="8583295"/>
+          <a:ext cx="1150907" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing29.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207E1752-AD05-4758-8A34-E66012E793BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="9030970"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1332866</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>989172</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A5680EE-8830-C063-C536-663C4AC28698}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1399541" y="9040495"/>
+          <a:ext cx="1161256" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48CE25D9-F129-4B8C-477F-839EA152E49A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="9259570"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1247140</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>896907</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9529F85-8E9A-11C4-0FEC-C5105150B00E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1313815" y="9265285"/>
+          <a:ext cx="1154717" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215315</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1555114</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE1248CA-E938-F0FE-9BAB-E8C5DD27F697}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8802369"/>
+          <a:ext cx="1158800" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1250950</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>908337</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CB28107-A765-5CAA-EF80-70866E2F6363}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1317625" y="8808085"/>
+          <a:ext cx="1162337" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D9B63BA-0CEA-D867-664A-094CA1D07CB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="8345170"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1273810</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>921672</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718127DA-30D8-17E2-6C74-47F3AE268674}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1340485" y="8350885"/>
+          <a:ext cx="1152812" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EFA0E6D-83C3-6E73-2F25-6A684415C1F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8573770"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing33.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71344CBC-AF68-919D-AFBC-E5E2D53FC269}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8573770"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1336675</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>990252</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46EF73A3-5CA5-3926-330E-5D44212F8BA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1403350" y="8583295"/>
+          <a:ext cx="1158527" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing34.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46C13ABC-2425-7E76-DBC9-A8EB301E573D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="8116570"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1302385</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>942627</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9BB0D64-3AD7-EDB2-07EC-336CC7EAD683}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1369060" y="8126095"/>
+          <a:ext cx="1145192" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing35.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215315</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1555114</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614E9B69-A426-9FAE-B5C1-C101CEBDED10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8802369"/>
+          <a:ext cx="1158800" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1279526</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>935832</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07EE0EE0-B892-FB6E-D99A-0D386BB3DB05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1346201" y="8811895"/>
+          <a:ext cx="1161256" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing36.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214765</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA284A5E-8C7C-65A5-DC86-BD369EA26138}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8345170"/>
+          <a:ext cx="1158250" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1374775</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1022637</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D1B359F-6F10-5DDC-94C4-48B81A3CBDE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1441450" y="8350885"/>
+          <a:ext cx="1152812" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing37.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214765</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA217B4-25F0-21E8-A494-F750C1809638}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8573770"/>
+          <a:ext cx="1158250" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1344294</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1000451</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8449B670-1059-1254-B80F-4412B77F47BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1410969" y="8579485"/>
+          <a:ext cx="1161107" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B9ED2C1-2A69-0B5B-5019-84E915E206EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9259570"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing39.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F58FF530-DC92-4763-7F7F-67DFCB1E6313}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8116570"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214765</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13920F7A-E7FB-BC09-1822-733A5F4F3C11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="10402570"/>
+          <a:ext cx="1158250" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1237615</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>895002</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1543685</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03DE3DD4-9991-8590-001A-2C6C55003F55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1304290" y="10402570"/>
+          <a:ext cx="1162337" cy="1532890"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>921385</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>306357</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1543685</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAB00D14-2269-F8D3-78BA-225B22880450}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2493010" y="10402570"/>
+          <a:ext cx="1166147" cy="1532890"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>78016</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>16509</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1224826</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>1545589</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagem 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFDEDDBE-A1F5-BD65-56FF-906992EC2FCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="143065" y="12241033"/>
+          <a:ext cx="1146810" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>46327</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1222562</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>1543685</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92C27344-F937-22D5-46A4-5DE90D21EAB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="112588" y="14174718"/>
+          <a:ext cx="1176235" cy="1540510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>86495</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605046</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagem 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28B9BD46-9B22-0E52-8D3A-1837E76C8CD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4260930" y="10431559"/>
+          <a:ext cx="1206007" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11387450-C9CC-1CCC-FFAE-7533E1D13A1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8345170"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>117475</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>6985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1266477</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1536065</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D692074-5642-C6C5-CE46-F85F3420E47F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="184150" y="8112760"/>
+          <a:ext cx="1149002" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1372871</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1029177</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1532255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5AF27A8-CDCD-FCE3-4AFE-54AAB877BC0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1439546" y="8116570"/>
+          <a:ext cx="1161256" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60326</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1208247</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B686988-1C49-E02A-5FC6-063E7A8E38DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="127001" y="9493885"/>
+          <a:ext cx="1147921" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60325</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>7564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1235997</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1572839</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A192E84-7577-4F21-2422-76E86242DA3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="126586" y="11371303"/>
+          <a:ext cx="1175672" cy="1565275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>57180</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>575838</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagem 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3BFEF6E-3486-45CA-F4FC-FF2CA36A681C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4231615" y="9500097"/>
+          <a:ext cx="1206114" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1295671</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>8226</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>953526</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1537306</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagem 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96104FF2-4350-D66B-5229-8D299413F24D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1361932" y="11371965"/>
+          <a:ext cx="1165290" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1267680</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>15846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>962822</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1541116</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagem 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26FE29A8-0D52-3E5A-1AB5-C3C01E862EF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1333941" y="9499433"/>
+          <a:ext cx="1202577" cy="1525270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A882729-7910-2607-0790-CD152E57EB86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="8345170"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1245236</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>901542</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1532255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5602229-6E34-CC13-BD30-F05A059DFE10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1311911" y="8345170"/>
+          <a:ext cx="1161256" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56514</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>8889</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1213944</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1553209</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B60E20F-2607-BE50-6887-E04675BEC461}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123189" y="10219689"/>
+          <a:ext cx="1157430" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214272</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1547495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagem 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93645F2-2306-0314-9DAB-7F4F4EB15761}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="12090400"/>
+          <a:ext cx="1157757" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>92709</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>16509</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>562980</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1545589</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC21D60D-426C-6E53-AC7D-AF6B848F14A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4264659" y="8350884"/>
+          <a:ext cx="1156071" cy="1529080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CA46A51-61BB-B143-9B2B-2566FB42708B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8573770"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1239520</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>896907</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1532255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46D3CF26-3C54-31FA-AEC7-A37EAECEE19B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1306195" y="8573770"/>
+          <a:ext cx="1162337" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215042</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A18FF83-5F56-CAEE-E876-D0BC38EC06DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="9030970"/>
+          <a:ext cx="1158527" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56516</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215867</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFFD68E-85EB-0F24-E809-B51233168A46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123191" y="9488170"/>
+          <a:ext cx="1159351" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1250949</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>908263</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1541780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCD0A083-2C32-138A-990B-04487E0AD8A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1317624" y="9497695"/>
+          <a:ext cx="1162264" cy="1521460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>8890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1215701</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1553210</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA2B831D-FA7D-5C42-9485-26CA88908998}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="11362690"/>
+          <a:ext cx="1159186" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214272</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1547495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagem 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C9937E1-AC1E-982D-409F-CB3C0D1D3F0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="13233400"/>
+          <a:ext cx="1157757" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1214418</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1555115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CBBFA2A-DB31-40E6-1CF2-8E1BBC02948A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123190" y="8345170"/>
+          <a:ext cx="1157903" cy="1544320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1256665</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>908337</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1545590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AAE57D5-085B-9B57-11BE-D37E3EDC2D72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1323340" y="8350885"/>
+          <a:ext cx="1156622" cy="1529080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3449,10 +6742,11 @@
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="11" width="14" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3563,7 +6857,9 @@
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -3581,7 +6877,9 @@
       <c r="D10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="27" t="s">
+        <v>343</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="27"/>
       <c r="H10" s="27"/>
@@ -3600,7 +6898,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="27"/>
@@ -3620,12 +6918,18 @@
         <v>29</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="27"/>
+        <v>344</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>348</v>
+      </c>
       <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
+      <c r="I12" s="27" t="s">
+        <v>348</v>
+      </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
     </row>
@@ -3640,12 +6944,18 @@
         <v>31</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="27"/>
+        <v>346</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>348</v>
+      </c>
       <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
+      <c r="I13" s="27" t="s">
+        <v>348</v>
+      </c>
       <c r="J13" s="27"/>
       <c r="K13" s="4"/>
     </row>
@@ -3660,7 +6970,7 @@
         <v>33</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="27"/>
@@ -3679,7 +6989,9 @@
       <c r="D15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="27"/>
+      <c r="E15" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="27"/>
       <c r="H15" s="4"/>
@@ -3698,12 +7010,16 @@
         <v>33</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>348</v>
+      </c>
       <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>348</v>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -3718,7 +7034,7 @@
         <v>38</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -3737,7 +7053,9 @@
       <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="27"/>
+      <c r="E18" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="F18" s="3"/>
       <c r="G18" s="27"/>
       <c r="H18" s="27"/>
@@ -3756,12 +7074,18 @@
         <v>42</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="27"/>
+        <v>347</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
+      <c r="I19" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
@@ -3775,7 +7099,9 @@
       <c r="D20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="F20" s="4"/>
       <c r="G20" s="6" t="s">
         <v>333</v>
@@ -3787,7 +7113,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>46</v>
       </c>
@@ -3798,10 +7124,14 @@
         <v>47</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+        <v>352</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>348</v>
+      </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -3818,13 +7148,13 @@
         <v>50</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>48</v>
@@ -3846,7 +7176,7 @@
         <v>53</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -3867,9 +7197,13 @@
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="27"/>
+      <c r="G24" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
+      <c r="I24" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
@@ -3883,7 +7217,9 @@
       <c r="D25" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="27"/>
+      <c r="E25" s="27" t="s">
+        <v>343</v>
+      </c>
       <c r="F25" s="3"/>
       <c r="G25" s="27"/>
       <c r="H25" s="27"/>
@@ -3938,7 +7274,7 @@
         <v>64</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -3958,7 +7294,7 @@
         <v>66</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -3978,7 +7314,7 @@
         <v>57</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="27"/>
@@ -3998,7 +7334,7 @@
         <v>24</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="4"/>
@@ -4018,12 +7354,16 @@
         <v>70</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="27"/>
+      <c r="G32" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
+      <c r="I32" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
     </row>
@@ -4037,7 +7377,9 @@
       <c r="D33" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E33" s="27"/>
+      <c r="E33" s="27" t="s">
+        <v>335</v>
+      </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -4055,7 +7397,9 @@
       <c r="D34" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="27"/>
+      <c r="E34" s="54" t="s">
+        <v>340</v>
+      </c>
       <c r="F34" s="3"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -4073,7 +7417,9 @@
       <c r="D35" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E35" s="27"/>
+      <c r="E35" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -4092,7 +7438,7 @@
         <v>78</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="27"/>
@@ -4129,7 +7475,9 @@
       <c r="D38" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="27"/>
+      <c r="E38" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -4148,7 +7496,7 @@
         <v>82</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -4168,7 +7516,7 @@
         <v>84</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="27"/>
@@ -4188,7 +7536,7 @@
         <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="27"/>
@@ -4208,7 +7556,7 @@
         <v>72</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -4245,7 +7593,9 @@
       <c r="D44" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E44" s="27"/>
+      <c r="E44" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F44" s="3"/>
       <c r="G44" s="27"/>
       <c r="H44" s="27"/>
@@ -4264,7 +7614,7 @@
         <v>84</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -4283,7 +7633,9 @@
       <c r="D46" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="F46" s="3"/>
       <c r="G46" s="27"/>
       <c r="H46" s="27"/>
@@ -4302,7 +7654,7 @@
         <v>40</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -4322,7 +7674,7 @@
         <v>84</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -4342,7 +7694,7 @@
         <v>40</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="27"/>
@@ -4361,7 +7713,9 @@
       <c r="D50" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="27"/>
+      <c r="E50" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F50" s="3"/>
       <c r="G50" s="27"/>
       <c r="H50" s="4"/>
@@ -4379,7 +7733,9 @@
       <c r="D51" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="27"/>
+      <c r="E51" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F51" s="3"/>
       <c r="G51" s="27"/>
       <c r="H51" s="4"/>
@@ -4397,7 +7753,9 @@
       <c r="D52" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="27"/>
+      <c r="E52" s="27" t="s">
+        <v>340</v>
+      </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -4415,7 +7773,9 @@
       <c r="D53" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="6"/>
+      <c r="E53" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -4433,9 +7793,13 @@
       <c r="D54" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E54" s="27"/>
+      <c r="E54" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="F54" s="3"/>
-      <c r="G54" s="27"/>
+      <c r="G54" s="27" t="s">
+        <v>349</v>
+      </c>
       <c r="H54" s="27"/>
       <c r="I54" s="27"/>
       <c r="J54" s="4"/>
@@ -4800,7 +8164,7 @@
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
       <c r="G22" s="37" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H22" s="38"/>
     </row>
@@ -4827,7 +8191,9 @@
       </c>
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
-      <c r="G24" s="38"/>
+      <c r="G24" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H24" s="38"/>
     </row>
     <row r="25" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4853,7 +8219,9 @@
       </c>
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
-      <c r="G26" s="38"/>
+      <c r="G26" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H26" s="38"/>
     </row>
     <row r="27" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4983,9 +8351,7 @@
       <c r="H39" s="44"/>
     </row>
     <row r="40" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B40" s="45"/>
       <c r="C40" s="45"/>
       <c r="D40" s="45"/>
       <c r="E40" s="45" t="s">
@@ -5009,9 +8375,7 @@
       <c r="H41" s="44"/>
     </row>
     <row r="42" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B42" s="45"/>
       <c r="C42" s="45"/>
       <c r="D42" s="45"/>
       <c r="E42" s="45" t="s">
@@ -5337,7 +8701,7 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H17" s="38"/>
     </row>
@@ -5855,7 +9219,9 @@
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="G16" s="38" t="s">
+        <v>338</v>
+      </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6013,9 +9379,7 @@
       <c r="H31" s="44"/>
     </row>
     <row r="32" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B32" s="45"/>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
       <c r="E32" s="45" t="s">
@@ -6159,6 +9523,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6171,7 +9536,7 @@
     <col min="1" max="1" width="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
@@ -6239,7 +9604,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
     </row>
-    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B8" s="15" t="s">
         <v>118</v>
       </c>
@@ -6496,7 +9861,7 @@
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
       <c r="G22" s="38" t="s">
-        <v>43</v>
+        <v>347</v>
       </c>
       <c r="H22" s="38"/>
     </row>
@@ -6510,7 +9875,9 @@
       </c>
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
-      <c r="G23" s="38"/>
+      <c r="G23" s="37" t="s">
+        <v>348</v>
+      </c>
       <c r="H23" s="38"/>
     </row>
     <row r="24" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6523,7 +9890,9 @@
       </c>
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
-      <c r="G24" s="38"/>
+      <c r="G24" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H24" s="38"/>
     </row>
     <row r="25" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6549,7 +9918,9 @@
       </c>
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
-      <c r="G26" s="38"/>
+      <c r="G26" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H26" s="38"/>
     </row>
     <row r="27" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6679,9 +10050,7 @@
       <c r="H39" s="44"/>
     </row>
     <row r="40" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B40" s="45"/>
       <c r="C40" s="45"/>
       <c r="D40" s="45"/>
       <c r="E40" s="45" t="s">
@@ -6705,9 +10074,7 @@
       <c r="H41" s="44"/>
     </row>
     <row r="42" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B42" s="45"/>
       <c r="C42" s="45"/>
       <c r="D42" s="45"/>
       <c r="E42" s="45" t="s">
@@ -7192,7 +10559,9 @@
       </c>
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
-      <c r="G26" s="38"/>
+      <c r="G26" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H26" s="38"/>
     </row>
     <row r="27" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7218,9 +10587,7 @@
       </c>
       <c r="E28" s="36"/>
       <c r="F28" s="36"/>
-      <c r="G28" s="37" t="s">
-        <v>333</v>
-      </c>
+      <c r="G28" s="37"/>
       <c r="H28" s="38"/>
     </row>
     <row r="29" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7246,9 +10613,7 @@
       </c>
       <c r="E30" s="36"/>
       <c r="F30" s="36"/>
-      <c r="G30" s="37" t="s">
-        <v>333</v>
-      </c>
+      <c r="G30" s="37"/>
       <c r="H30" s="38"/>
     </row>
     <row r="31" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7354,9 +10719,7 @@
       <c r="H41" s="44"/>
     </row>
     <row r="42" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B42" s="45"/>
       <c r="C42" s="45"/>
       <c r="D42" s="45"/>
       <c r="E42" s="45" t="s">
@@ -7500,6 +10863,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7693,7 +11057,7 @@
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
       <c r="G15" s="38" t="s">
-        <v>48</v>
+        <v>351</v>
       </c>
       <c r="H15" s="38"/>
     </row>
@@ -7707,7 +11071,9 @@
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="G16" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7720,7 +11086,9 @@
       </c>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="38"/>
+      <c r="G17" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H17" s="38"/>
     </row>
     <row r="18" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7746,7 +11114,9 @@
       </c>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="38"/>
+      <c r="G19" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H19" s="38"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7851,7 +11221,7 @@
       <c r="G30" s="44"/>
       <c r="H30" s="44"/>
     </row>
-    <row r="31" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="251.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="45"/>
       <c r="C31" s="45"/>
       <c r="D31" s="45"/>
@@ -7876,14 +11246,10 @@
       <c r="H32" s="44"/>
     </row>
     <row r="33" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B33" s="45"/>
       <c r="C33" s="45"/>
       <c r="D33" s="45"/>
-      <c r="E33" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="E33" s="45"/>
       <c r="F33" s="45"/>
       <c r="G33" s="45"/>
       <c r="H33" s="45"/>
@@ -7902,9 +11268,7 @@
       <c r="H34" s="44"/>
     </row>
     <row r="35" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B35" s="45"/>
       <c r="C35" s="45"/>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -8442,7 +11806,7 @@
       <c r="E29" s="36"/>
       <c r="F29" s="36"/>
       <c r="G29" s="37" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H29" s="38"/>
     </row>
@@ -8472,7 +11836,7 @@
       <c r="E31" s="36"/>
       <c r="F31" s="36"/>
       <c r="G31" s="38" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="H31" s="38"/>
     </row>
@@ -8502,7 +11866,7 @@
       <c r="E33" s="36"/>
       <c r="F33" s="36"/>
       <c r="G33" s="38" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="H33" s="38"/>
     </row>
@@ -9000,7 +12364,7 @@
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H18" s="38"/>
     </row>
@@ -9582,7 +12946,9 @@
       </c>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
-      <c r="G20" s="38"/>
+      <c r="G20" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H20" s="38"/>
     </row>
     <row r="21" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9608,7 +12974,9 @@
       </c>
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
-      <c r="G22" s="38"/>
+      <c r="G22" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H22" s="38"/>
     </row>
     <row r="23" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9740,9 +13108,7 @@
       <c r="H35" s="44"/>
     </row>
     <row r="36" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B36" s="45"/>
       <c r="C36" s="45"/>
       <c r="D36" s="45"/>
       <c r="E36" s="45" t="s">
@@ -9766,9 +13132,7 @@
       <c r="H37" s="44"/>
     </row>
     <row r="38" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B38" s="45"/>
       <c r="C38" s="45"/>
       <c r="D38" s="45"/>
       <c r="E38" s="45" t="s">
@@ -9860,6 +13224,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10136,7 +13501,9 @@
       </c>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="38"/>
+      <c r="G19" s="38" t="s">
+        <v>343</v>
+      </c>
       <c r="H19" s="38"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10294,9 +13661,7 @@
       <c r="H34" s="44"/>
     </row>
     <row r="35" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B35" s="45"/>
       <c r="C35" s="45"/>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -10440,6 +13805,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -41774,7 +45140,7 @@
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="37" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H20" s="38"/>
     </row>
@@ -41933,9 +45299,7 @@
       <c r="H35" s="44"/>
     </row>
     <row r="36" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B36" s="45"/>
       <c r="C36" s="45"/>
       <c r="D36" s="45"/>
       <c r="E36" s="45" t="s">
@@ -42079,6 +45443,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -42346,7 +45711,7 @@
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
       <c r="G19" s="37" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="38"/>
     </row>
@@ -42505,9 +45870,7 @@
       <c r="H34" s="44"/>
     </row>
     <row r="35" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B35" s="45"/>
       <c r="C35" s="45"/>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -42651,6 +46014,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -42980,7 +46344,7 @@
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
       <c r="G22" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H22" s="38"/>
     </row>
@@ -43573,7 +46937,7 @@
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="38" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="H20" s="38"/>
     </row>
@@ -44112,7 +47476,7 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="37" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="H17" s="38"/>
     </row>
@@ -44139,7 +47503,9 @@
       </c>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="38"/>
+      <c r="G19" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H19" s="38"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -44165,7 +47531,9 @@
       </c>
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
-      <c r="G21" s="38"/>
+      <c r="G21" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H21" s="38"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -44297,9 +47665,7 @@
       <c r="H34" s="44"/>
     </row>
     <row r="35" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B35" s="45"/>
       <c r="C35" s="45"/>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -44323,9 +47689,7 @@
       <c r="H36" s="44"/>
     </row>
     <row r="37" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B37" s="45"/>
       <c r="C37" s="45"/>
       <c r="D37" s="45"/>
       <c r="E37" s="45" t="s">
@@ -44628,7 +47992,9 @@
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="G16" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -44786,9 +48152,7 @@
       <c r="H31" s="44"/>
     </row>
     <row r="32" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B32" s="45"/>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
       <c r="E32" s="45" t="s">
@@ -44932,6 +48296,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -44947,7 +48312,7 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -45144,7 +48509,9 @@
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="G16" s="37" t="s">
+        <v>340</v>
+      </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -45302,9 +48669,7 @@
       <c r="H31" s="44"/>
     </row>
     <row r="32" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B32" s="45"/>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
       <c r="E32" s="45" t="s">
@@ -45448,6 +48813,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -45460,7 +48826,7 @@
     <col min="1" max="1" width="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
@@ -45676,7 +49042,9 @@
       </c>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="38"/>
+      <c r="G17" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H17" s="38"/>
     </row>
     <row r="18" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -45834,9 +49202,7 @@
       <c r="H32" s="44"/>
     </row>
     <row r="33" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B33" s="45"/>
       <c r="C33" s="45"/>
       <c r="D33" s="45"/>
       <c r="E33" s="45" t="s">
@@ -45980,6 +49346,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -45991,11 +49358,11 @@
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
     <col min="9" max="9" width="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -46266,7 +49633,9 @@
       </c>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
-      <c r="G20" s="38"/>
+      <c r="G20" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H20" s="38"/>
     </row>
     <row r="21" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -46568,6 +49937,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -46879,7 +50249,7 @@
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
       <c r="G21" s="37" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="H21" s="38"/>
     </row>
@@ -48053,7 +51423,9 @@
       </c>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="38"/>
+      <c r="G19" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H19" s="38"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -48211,9 +51583,7 @@
       <c r="H34" s="44"/>
     </row>
     <row r="35" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B35" s="45"/>
       <c r="C35" s="45"/>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -48357,6 +51727,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -48610,7 +51981,7 @@
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H18" s="38"/>
     </row>
@@ -49201,7 +52572,7 @@
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H20" s="38"/>
     </row>
@@ -49776,7 +53147,7 @@
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
       <c r="G19" s="37" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="H19" s="38"/>
     </row>
@@ -50317,7 +53688,7 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H17" s="38"/>
     </row>
@@ -51407,7 +54778,9 @@
       </c>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
-      <c r="G18" s="38"/>
+      <c r="G18" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H18" s="38"/>
     </row>
     <row r="19" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -51565,9 +54938,7 @@
       <c r="H33" s="44"/>
     </row>
     <row r="34" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B34" s="45"/>
       <c r="C34" s="45"/>
       <c r="D34" s="45"/>
       <c r="E34" s="45" t="s">
@@ -51711,6 +55082,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -51962,7 +55334,7 @@
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H18" s="38"/>
     </row>
@@ -52600,7 +55972,9 @@
       </c>
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
-      <c r="G22" s="38"/>
+      <c r="G22" s="37" t="s">
+        <v>343</v>
+      </c>
       <c r="H22" s="38"/>
     </row>
     <row r="23" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -52758,9 +56132,7 @@
       <c r="H37" s="44"/>
     </row>
     <row r="38" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B38" s="45"/>
       <c r="C38" s="45"/>
       <c r="D38" s="45"/>
       <c r="E38" s="45" t="s">
@@ -52904,6 +56276,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -53114,7 +56487,9 @@
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="G16" s="38" t="s">
+        <v>335</v>
+      </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -53684,7 +57059,7 @@
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
       <c r="G19" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H19" s="38"/>
     </row>
@@ -54221,7 +57596,7 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="37" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="H17" s="38"/>
     </row>
@@ -54774,7 +58149,7 @@
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="37" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="H18" s="38"/>
     </row>
@@ -55378,7 +58753,9 @@
       </c>
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
-      <c r="G21" s="38"/>
+      <c r="G21" s="37" t="s">
+        <v>340</v>
+      </c>
       <c r="H21" s="38"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -55536,9 +58913,7 @@
       <c r="H36" s="44"/>
     </row>
     <row r="37" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B37" s="45"/>
       <c r="C37" s="45"/>
       <c r="D37" s="45"/>
       <c r="E37" s="45" t="s">
@@ -55682,6 +59057,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -55892,7 +59268,9 @@
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="38"/>
+      <c r="G16" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -56050,9 +59428,7 @@
       <c r="H31" s="44"/>
     </row>
     <row r="32" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B32" s="45"/>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
       <c r="E32" s="45" t="s">
@@ -56196,6 +59572,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -56424,7 +59801,9 @@
       </c>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="38"/>
+      <c r="G17" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H17" s="38"/>
     </row>
     <row r="18" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -56582,9 +59961,7 @@
       <c r="H32" s="44"/>
     </row>
     <row r="33" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B33" s="45"/>
       <c r="C33" s="45"/>
       <c r="D33" s="45"/>
       <c r="E33" s="45" t="s">
@@ -56728,6 +60105,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -56743,7 +60121,7 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -56939,7 +60317,7 @@
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
       <c r="G16" s="37" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H16" s="38"/>
     </row>
@@ -57098,9 +60476,7 @@
       <c r="H31" s="44"/>
     </row>
     <row r="32" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B32" s="45"/>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
       <c r="E32" s="45" t="s">
@@ -57244,6 +60620,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -57578,7 +60955,9 @@
       </c>
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
-      <c r="G22" s="38"/>
+      <c r="G22" s="37" t="s">
+        <v>338</v>
+      </c>
       <c r="H22" s="38"/>
     </row>
     <row r="23" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -57591,7 +60970,9 @@
       </c>
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
-      <c r="G23" s="38"/>
+      <c r="G23" s="38" t="s">
+        <v>343</v>
+      </c>
       <c r="H23" s="38"/>
     </row>
     <row r="24" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -57604,7 +60985,9 @@
       </c>
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
-      <c r="G24" s="38"/>
+      <c r="G24" s="38" t="s">
+        <v>350</v>
+      </c>
       <c r="H24" s="38"/>
     </row>
     <row r="25" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -57736,9 +61119,7 @@
       <c r="H37" s="44"/>
     </row>
     <row r="38" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B38" s="45"/>
       <c r="C38" s="45"/>
       <c r="D38" s="45"/>
       <c r="E38" s="45" t="s">
@@ -57762,9 +61143,7 @@
       <c r="H39" s="44"/>
     </row>
     <row r="40" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B40" s="45"/>
       <c r="C40" s="45"/>
       <c r="D40" s="45"/>
       <c r="E40" s="45" t="s">
@@ -57882,6 +61261,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -58193,7 +61573,7 @@
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
       <c r="G21" s="37" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H21" s="38"/>
     </row>
@@ -58894,7 +62274,7 @@
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
       <c r="G26" s="37" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="H26" s="38"/>
     </row>
@@ -58908,7 +62288,9 @@
       </c>
       <c r="E27" s="36"/>
       <c r="F27" s="36"/>
-      <c r="G27" s="38"/>
+      <c r="G27" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H27" s="38"/>
     </row>
     <row r="28" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -58921,7 +62303,9 @@
       </c>
       <c r="E28" s="36"/>
       <c r="F28" s="36"/>
-      <c r="G28" s="38"/>
+      <c r="G28" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H28" s="38"/>
     </row>
     <row r="29" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -58947,7 +62331,9 @@
       </c>
       <c r="E30" s="36"/>
       <c r="F30" s="36"/>
-      <c r="G30" s="38"/>
+      <c r="G30" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H30" s="38"/>
     </row>
     <row r="31" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -59077,9 +62463,7 @@
       <c r="H43" s="44"/>
     </row>
     <row r="44" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B44" s="45"/>
       <c r="C44" s="45"/>
       <c r="D44" s="45"/>
       <c r="E44" s="45" t="s">
@@ -59103,9 +62487,7 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B46" s="45"/>
       <c r="C46" s="45"/>
       <c r="D46" s="45"/>
       <c r="E46" s="45" t="s">
@@ -59433,7 +62815,7 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="37" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="H17" s="38"/>
     </row>
@@ -59447,7 +62829,9 @@
       </c>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
-      <c r="G18" s="38"/>
+      <c r="G18" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H18" s="38"/>
     </row>
     <row r="19" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -59460,7 +62844,9 @@
       </c>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="38"/>
+      <c r="G19" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H19" s="38"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -59486,7 +62872,9 @@
       </c>
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
-      <c r="G21" s="38"/>
+      <c r="G21" s="38" t="s">
+        <v>348</v>
+      </c>
       <c r="H21" s="38"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -59618,9 +63006,7 @@
       <c r="H34" s="44"/>
     </row>
     <row r="35" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B35" s="45"/>
       <c r="C35" s="45"/>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -59644,9 +63030,7 @@
       <c r="H36" s="44"/>
     </row>
     <row r="37" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B37" s="45"/>
       <c r="C37" s="45"/>
       <c r="D37" s="45"/>
       <c r="E37" s="45" t="s">
@@ -59754,7 +63138,7 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -59988,7 +63372,7 @@
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="37" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H18" s="38"/>
     </row>
@@ -60582,7 +63966,9 @@
       </c>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
-      <c r="G20" s="38"/>
+      <c r="G20" s="38" t="s">
+        <v>340</v>
+      </c>
       <c r="H20" s="38"/>
     </row>
     <row r="21" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -60740,9 +64126,7 @@
       <c r="H35" s="44"/>
     </row>
     <row r="36" spans="2:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="45" t="s">
-        <v>163</v>
-      </c>
+      <c r="B36" s="45"/>
       <c r="C36" s="45"/>
       <c r="D36" s="45"/>
       <c r="E36" s="45" t="s">
@@ -60886,5 +64270,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>